--- a/artfynd/A 58236-2025 artfynd.xlsx
+++ b/artfynd/A 58236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120530511</v>
+        <v>120530507</v>
       </c>
       <c r="B2" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524610</v>
+        <v>524687</v>
       </c>
       <c r="R2" t="n">
-        <v>7112816</v>
+        <v>7112804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120530509</v>
+        <v>120530511</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524673</v>
+        <v>524610</v>
       </c>
       <c r="R3" t="n">
-        <v>7112830</v>
+        <v>7112816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120530507</v>
+        <v>120530508</v>
       </c>
       <c r="B4" t="n">
-        <v>82378</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,12 +969,7 @@
         <v>120530512</v>
       </c>
       <c r="B5" t="n">
-        <v>79704</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,108 +1060,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>120530508</v>
-      </c>
-      <c r="B6" t="n">
-        <v>74702</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ringvattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>524687</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7112804</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58236-2025 artfynd.xlsx
+++ b/artfynd/A 58236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530507</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530511</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>